--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33D84C9F-5898-4EFD-8E64-B5B3CA8B7EC2}"/>
+  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BF5EE6-310E-4EE1-8D90-B1D0A8B34476}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="0" windowWidth="10260" windowHeight="12072" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -256,7 +256,7 @@
     <t>หอมหอย</t>
   </si>
   <si>
-    <t>GMMFAFA</t>
+    <t>Ducks</t>
   </si>
 </sst>
 </file>
@@ -712,12 +712,11 @@
       <c r="B2" s="5">
         <v>9692</v>
       </c>
-      <c r="C2" s="4">
-        <v>2592</v>
-      </c>
-      <c r="D2" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C2,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+      <c r="C2" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D2" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>5</v>
@@ -730,12 +729,11 @@
       <c r="B3" s="5">
         <v>5873</v>
       </c>
-      <c r="C3" s="4">
-        <v>2367</v>
-      </c>
-      <c r="D3" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C3,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+      <c r="C3" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D3" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>5</v>
@@ -752,7 +750,6 @@
         <v>#N/A</v>
       </c>
       <c r="D4" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C4,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -766,12 +763,11 @@
       <c r="B5" s="4">
         <v>8153</v>
       </c>
-      <c r="C5" s="4">
-        <v>2478</v>
-      </c>
-      <c r="D5" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C5,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum III</v>
+      <c r="C5" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D5" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>5</v>
@@ -784,12 +780,11 @@
       <c r="B6" s="4">
         <v>6654</v>
       </c>
-      <c r="C6" s="4">
-        <v>1222</v>
-      </c>
-      <c r="D6" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C6,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron III</v>
+      <c r="C6" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D6" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>5</v>
@@ -802,12 +797,11 @@
       <c r="B7" s="4">
         <v>5161</v>
       </c>
-      <c r="C7" s="4">
-        <v>1987</v>
-      </c>
-      <c r="D7" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C7,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold I</v>
+      <c r="C7" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D7" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>5</v>
@@ -824,7 +818,6 @@
         <v>#N/A</v>
       </c>
       <c r="D8" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C8,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -838,12 +831,11 @@
       <c r="B9" s="4">
         <v>804</v>
       </c>
-      <c r="C9" s="4">
-        <v>1000</v>
-      </c>
-      <c r="D9" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C9,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron I</v>
+      <c r="C9" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D9" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>5</v>
@@ -856,12 +848,11 @@
       <c r="B10" s="5">
         <v>7042</v>
       </c>
-      <c r="C10" s="4">
-        <v>2744</v>
-      </c>
-      <c r="D10" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C10,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond III</v>
+      <c r="C10" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D10" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>5</v>
@@ -874,12 +865,11 @@
       <c r="B11" s="5">
         <v>9706</v>
       </c>
-      <c r="C11" s="4">
-        <v>2579</v>
-      </c>
-      <c r="D11" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C11,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+      <c r="C11" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D11" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>5</v>
@@ -892,12 +882,11 @@
       <c r="B12" s="5">
         <v>5464</v>
       </c>
-      <c r="C12" s="4">
-        <v>2504</v>
-      </c>
-      <c r="D12" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C12,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+      <c r="C12" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D12" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>5</v>
@@ -910,12 +899,11 @@
       <c r="B13" s="4">
         <v>7449</v>
       </c>
-      <c r="C13" s="4">
-        <v>2245</v>
-      </c>
-      <c r="D13" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C13,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum I</v>
+      <c r="C13" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D13" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E13" s="5" t="s">
         <v>5</v>
@@ -928,12 +916,11 @@
       <c r="B14" s="4">
         <v>3480</v>
       </c>
-      <c r="C14" s="4">
-        <v>2163</v>
-      </c>
-      <c r="D14" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C14,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+      <c r="C14" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D14" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>5</v>
@@ -950,7 +937,6 @@
         <v>#N/A</v>
       </c>
       <c r="D15" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C15,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -964,12 +950,11 @@
       <c r="B16" s="5">
         <v>5078</v>
       </c>
-      <c r="C16" s="4">
-        <v>2497</v>
-      </c>
-      <c r="D16" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C16,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum III</v>
+      <c r="C16" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D16" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>5</v>
@@ -982,12 +967,11 @@
       <c r="B17" s="5">
         <v>4713</v>
       </c>
-      <c r="C17" s="4">
-        <v>1238</v>
-      </c>
-      <c r="D17" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C17,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Iron III</v>
+      <c r="C17" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D17" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>5</v>
@@ -1000,12 +984,11 @@
       <c r="B18" s="5">
         <v>6455</v>
       </c>
-      <c r="C18" s="4">
-        <v>2620</v>
-      </c>
-      <c r="D18" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C18,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond II</v>
+      <c r="C18" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D18" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>5</v>
@@ -1018,12 +1001,11 @@
       <c r="B19" s="4">
         <v>2886</v>
       </c>
-      <c r="C19" s="4">
-        <v>2011</v>
-      </c>
-      <c r="D19" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C19,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold II</v>
+      <c r="C19" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D19" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>5</v>
@@ -1036,12 +1018,11 @@
       <c r="B20" s="5">
         <v>1025</v>
       </c>
-      <c r="C20" s="4">
-        <v>2228</v>
-      </c>
-      <c r="D20" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C20,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum I</v>
+      <c r="C20" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D20" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>5</v>
@@ -1054,12 +1035,11 @@
       <c r="B21" s="4">
         <v>3528</v>
       </c>
-      <c r="C21" s="4">
-        <v>2187</v>
-      </c>
-      <c r="D21" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C21,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Gold III</v>
+      <c r="C21" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D21" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>5</v>
@@ -1072,12 +1052,11 @@
       <c r="B22" s="4">
         <v>168</v>
       </c>
-      <c r="C22" s="4">
-        <v>2380</v>
-      </c>
-      <c r="D22" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C22,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum II</v>
+      <c r="C22" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D22" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>5</v>
@@ -1090,12 +1069,11 @@
       <c r="B23" s="5">
         <v>5101</v>
       </c>
-      <c r="C23" s="4">
-        <v>2410</v>
-      </c>
-      <c r="D23" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C23,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum III</v>
+      <c r="C23" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D23" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>5</v>
@@ -1112,7 +1090,6 @@
         <v>#N/A</v>
       </c>
       <c r="D24" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C24,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -1126,12 +1103,11 @@
       <c r="B25" s="4">
         <v>6698</v>
       </c>
-      <c r="C25" s="4">
-        <v>1662</v>
-      </c>
-      <c r="D25" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C25,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Silver I</v>
+      <c r="C25" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D25" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>5</v>
@@ -1144,12 +1120,11 @@
       <c r="B26" s="5">
         <v>8128</v>
       </c>
-      <c r="C26" s="4">
-        <v>2811</v>
-      </c>
-      <c r="D26" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C26,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Master I</v>
+      <c r="C26" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>5</v>
@@ -1166,7 +1141,6 @@
         <v>#N/A</v>
       </c>
       <c r="D27" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C27,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -1180,12 +1154,11 @@
       <c r="B28" s="4">
         <v>452</v>
       </c>
-      <c r="C28" s="4">
-        <v>2624</v>
-      </c>
-      <c r="D28" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C28,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond II</v>
+      <c r="C28" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D28" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>5</v>
@@ -1198,12 +1171,11 @@
       <c r="B29" s="4">
         <v>9881</v>
       </c>
-      <c r="C29" s="4">
-        <v>2287</v>
-      </c>
-      <c r="D29" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C29,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Platinum I</v>
+      <c r="C29" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D29" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>5</v>
@@ -1216,12 +1188,11 @@
       <c r="B30" s="5">
         <v>7411</v>
       </c>
-      <c r="C30" s="4">
-        <v>2503</v>
-      </c>
-      <c r="D30" s="4" t="str">
-        <f>_xlfn.XLOOKUP(C30,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
-        <v>Diamond I</v>
+      <c r="C30" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D30" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>5</v>
@@ -1234,11 +1205,10 @@
       <c r="B31" s="5">
         <v>5566</v>
       </c>
-      <c r="C31" s="4">
-        <v>0</v>
+      <c r="C31" s="4" t="e">
+        <v>#N/A</v>
       </c>
       <c r="D31" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C31,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E31" s="5" t="s">
@@ -1256,7 +1226,6 @@
         <v>#N/A</v>
       </c>
       <c r="D32" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C32,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E32" s="5" t="s">
@@ -1274,7 +1243,6 @@
         <v>#N/A</v>
       </c>
       <c r="D33" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C33,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E33" s="5" t="s">
@@ -1292,7 +1260,6 @@
         <v>#N/A</v>
       </c>
       <c r="D34" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C34,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E34" s="5" t="s">
@@ -1310,7 +1277,6 @@
         <v>#N/A</v>
       </c>
       <c r="D35" s="4" t="e">
-        <f>_xlfn.XLOOKUP(C35,RTA_Rank!B:B,RTA_Rank!A:A,,-1)</f>
         <v>#N/A</v>
       </c>
       <c r="E35" s="5" t="s">

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="160" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BF5EE6-310E-4EE1-8D90-B1D0A8B34476}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996DE1C3-7406-4878-9F8E-8E2738B8AC22}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
   <si>
     <t>Name</t>
   </si>
@@ -121,12 +121,6 @@
     <t>SekiSaySo</t>
   </si>
   <si>
-    <t>soutax</t>
-  </si>
-  <si>
-    <t>Catzilla</t>
-  </si>
-  <si>
     <t>Sora</t>
   </si>
   <si>
@@ -257,6 +251,18 @@
   </si>
   <si>
     <t>Ducks</t>
+  </si>
+  <si>
+    <t>Souta メ</t>
+  </si>
+  <si>
+    <t>iCatzilla</t>
+  </si>
+  <si>
+    <t>SwallowTaiL</t>
+  </si>
+  <si>
+    <t>N • Force1</t>
   </si>
 </sst>
 </file>
@@ -678,7 +684,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -741,7 +747,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5">
         <v>7351</v>
@@ -775,10 +781,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4">
-        <v>6654</v>
+        <v>5161</v>
       </c>
       <c r="C6" s="4" t="e">
         <v>#N/A</v>
@@ -792,10 +798,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4">
-        <v>5161</v>
+        <v>3194</v>
       </c>
       <c r="C7" s="4" t="e">
         <v>#N/A</v>
@@ -809,10 +815,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4">
-        <v>3194</v>
+        <v>804</v>
       </c>
       <c r="C8" s="4" t="e">
         <v>#N/A</v>
@@ -826,10 +832,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="4">
-        <v>804</v>
+        <v>14</v>
+      </c>
+      <c r="B9" s="5">
+        <v>7042</v>
       </c>
       <c r="C9" s="4" t="e">
         <v>#N/A</v>
@@ -843,10 +849,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5">
-        <v>7042</v>
+        <v>9706</v>
       </c>
       <c r="C10" s="4" t="e">
         <v>#N/A</v>
@@ -860,10 +866,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5">
-        <v>9706</v>
+        <v>5464</v>
       </c>
       <c r="C11" s="4" t="e">
         <v>#N/A</v>
@@ -877,10 +883,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="5">
-        <v>5464</v>
+        <v>31</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3480</v>
       </c>
       <c r="C12" s="4" t="e">
         <v>#N/A</v>
@@ -894,10 +900,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B13" s="4">
-        <v>7449</v>
+        <v>3481</v>
       </c>
       <c r="C13" s="4" t="e">
         <v>#N/A</v>
@@ -911,10 +917,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="4">
-        <v>3480</v>
+        <v>22</v>
+      </c>
+      <c r="B14" s="5">
+        <v>5078</v>
       </c>
       <c r="C14" s="4" t="e">
         <v>#N/A</v>
@@ -928,10 +934,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="4">
-        <v>3481</v>
+        <v>71</v>
+      </c>
+      <c r="B15" s="5">
+        <v>4713</v>
       </c>
       <c r="C15" s="4" t="e">
         <v>#N/A</v>
@@ -945,10 +951,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="5">
-        <v>5078</v>
+        <v>73</v>
+      </c>
+      <c r="B16" s="4">
+        <v>7449</v>
       </c>
       <c r="C16" s="4" t="e">
         <v>#N/A</v>
@@ -962,10 +968,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>73</v>
+        <v>17</v>
       </c>
       <c r="B17" s="5">
-        <v>4713</v>
+        <v>6455</v>
       </c>
       <c r="C17" s="4" t="e">
         <v>#N/A</v>
@@ -979,10 +985,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="5">
-        <v>6455</v>
+        <v>67</v>
+      </c>
+      <c r="B18" s="4">
+        <v>2886</v>
       </c>
       <c r="C18" s="4" t="e">
         <v>#N/A</v>
@@ -996,10 +1002,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B19" s="4">
-        <v>2886</v>
+        <v>21</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1025</v>
       </c>
       <c r="C19" s="4" t="e">
         <v>#N/A</v>
@@ -1013,10 +1019,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="5">
-        <v>1025</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="4">
+        <v>3528</v>
       </c>
       <c r="C20" s="4" t="e">
         <v>#N/A</v>
@@ -1030,10 +1036,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B21" s="4">
-        <v>3528</v>
+        <v>75</v>
+      </c>
+      <c r="B21" s="5">
+        <v>862</v>
       </c>
       <c r="C21" s="4" t="e">
         <v>#N/A</v>
@@ -1081,10 +1087,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4">
-        <v>2359</v>
+        <v>6698</v>
       </c>
       <c r="C24" s="4" t="e">
         <v>#N/A</v>
@@ -1098,10 +1104,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B25" s="4">
-        <v>6698</v>
+        <v>18</v>
+      </c>
+      <c r="B25" s="5">
+        <v>8128</v>
       </c>
       <c r="C25" s="4" t="e">
         <v>#N/A</v>
@@ -1115,10 +1121,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="5">
-        <v>8128</v>
+        <v>39</v>
+      </c>
+      <c r="B26" s="4">
+        <v>1004</v>
       </c>
       <c r="C26" s="4" t="e">
         <v>#N/A</v>
@@ -1132,10 +1138,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B27" s="4">
-        <v>1004</v>
+        <v>452</v>
       </c>
       <c r="C27" s="4" t="e">
         <v>#N/A</v>
@@ -1149,10 +1155,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B28" s="4">
-        <v>452</v>
+        <v>9881</v>
       </c>
       <c r="C28" s="4" t="e">
         <v>#N/A</v>
@@ -1166,10 +1172,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="4">
-        <v>9881</v>
+        <v>74</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2187</v>
       </c>
       <c r="C29" s="4" t="e">
         <v>#N/A</v>
@@ -1217,10 +1223,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="4">
-        <v>8334</v>
+        <v>6654</v>
       </c>
       <c r="C32" s="4" t="e">
         <v>#N/A</v>
@@ -1229,15 +1235,15 @@
         <v>#N/A</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="B33" s="4">
-        <v>7120</v>
+        <v>8334</v>
       </c>
       <c r="C33" s="4" t="e">
         <v>#N/A</v>
@@ -1246,15 +1252,15 @@
         <v>#N/A</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B34" s="4">
-        <v>3929</v>
+        <v>7120</v>
       </c>
       <c r="C34" s="4" t="e">
         <v>#N/A</v>
@@ -1263,34 +1269,69 @@
         <v>#N/A</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B35" s="4">
+        <v>2359</v>
+      </c>
+      <c r="C35" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D35" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="4">
+        <v>3929</v>
+      </c>
+      <c r="C36" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D36" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="4">
         <v>5297</v>
       </c>
-      <c r="C35" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D35" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>71</v>
+      <c r="C37" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D37" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A33:E35">
-    <sortCondition ref="A32:A35"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E31">
+    <sortCondition ref="A6:A31"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1355,15 +1396,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="7">
         <v>1000</v>
@@ -1371,7 +1412,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7">
         <v>1100</v>
@@ -1379,7 +1420,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" s="7">
         <v>1200</v>
@@ -1387,7 +1428,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" s="7">
         <v>1300</v>
@@ -1395,7 +1436,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" s="7">
         <v>1400</v>
@@ -1403,7 +1444,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="7">
         <v>1500</v>
@@ -1411,7 +1452,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" s="7">
         <v>1600</v>
@@ -1419,7 +1460,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" s="7">
         <v>1700</v>
@@ -1427,7 +1468,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7">
         <v>1800</v>
@@ -1435,7 +1476,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B11" s="7">
         <v>1900</v>
@@ -1443,7 +1484,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B12" s="7">
         <v>2000</v>
@@ -1451,7 +1492,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" s="7">
         <v>2100</v>
@@ -1459,7 +1500,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7">
         <v>2200</v>
@@ -1467,7 +1508,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7">
         <v>2300</v>
@@ -1475,7 +1516,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B16" s="7">
         <v>2400</v>
@@ -1483,7 +1524,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B17" s="7">
         <v>2500</v>
@@ -1491,7 +1532,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B18" s="7">
         <v>2600</v>
@@ -1499,7 +1540,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B19" s="7">
         <v>2700</v>
@@ -1507,7 +1548,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B20" s="7">
         <v>2800</v>
@@ -1515,7 +1556,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B21" s="7">
         <v>2900</v>
@@ -1523,7 +1564,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" s="7">
         <v>3000</v>
@@ -1531,7 +1572,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B23" s="7">
         <v>3100</v>
@@ -1539,7 +1580,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B24" s="7">
         <v>3500</v>
@@ -1547,7 +1588,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B25" s="7">
         <v>4000</v>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="189" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{996DE1C3-7406-4878-9F8E-8E2738B8AC22}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2E2C029-07E0-4899-8F46-416E6FCFAE16}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2652" yWindow="840" windowWidth="20388" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="77">
   <si>
     <t>Name</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>N • Force1</t>
+  </si>
+  <si>
+    <t>DUCKs</t>
   </si>
 </sst>
 </file>
@@ -684,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -815,10 +818,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B8" s="4">
-        <v>804</v>
+        <v>5055</v>
       </c>
       <c r="C8" s="4" t="e">
         <v>#N/A</v>
@@ -934,7 +937,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B15" s="5">
         <v>4713</v>
@@ -1223,10 +1226,10 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B32" s="4">
-        <v>6654</v>
+        <v>804</v>
       </c>
       <c r="C32" s="4" t="e">
         <v>#N/A</v>
@@ -1235,15 +1238,15 @@
         <v>#N/A</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B33" s="4">
-        <v>8334</v>
+        <v>6654</v>
       </c>
       <c r="C33" s="4" t="e">
         <v>#N/A</v>
@@ -1257,10 +1260,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B34" s="4">
-        <v>7120</v>
+        <v>8334</v>
       </c>
       <c r="C34" s="4" t="e">
         <v>#N/A</v>
@@ -1274,10 +1277,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B35" s="4">
-        <v>2359</v>
+        <v>7120</v>
       </c>
       <c r="C35" s="4" t="e">
         <v>#N/A</v>
@@ -1291,10 +1294,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="4">
-        <v>3929</v>
+        <v>2359</v>
       </c>
       <c r="C36" s="4" t="e">
         <v>#N/A</v>
@@ -1308,18 +1311,35 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="4">
+        <v>3929</v>
+      </c>
+      <c r="C37" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D37" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="4">
+      <c r="B38" s="4">
         <v>5297</v>
       </c>
-      <c r="C37" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D37" s="4" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E37" s="5" t="s">
+      <c r="C38" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D38" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>69</v>
       </c>
     </row>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2E2C029-07E0-4899-8F46-416E6FCFAE16}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC99DED-23D5-43D3-B57D-30F81CC1F1AF}"/>
   <bookViews>
-    <workbookView xWindow="2652" yWindow="840" windowWidth="20388" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -396,10 +396,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -903,10 +899,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="4">
-        <v>3481</v>
+        <v>22</v>
+      </c>
+      <c r="B13" s="5">
+        <v>5078</v>
       </c>
       <c r="C13" s="4" t="e">
         <v>#N/A</v>
@@ -920,10 +916,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
       <c r="B14" s="5">
-        <v>5078</v>
+        <v>4713</v>
       </c>
       <c r="C14" s="4" t="e">
         <v>#N/A</v>
@@ -937,10 +933,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B15" s="5">
-        <v>4713</v>
+        <v>73</v>
+      </c>
+      <c r="B15" s="4">
+        <v>7449</v>
       </c>
       <c r="C15" s="4" t="e">
         <v>#N/A</v>
@@ -954,10 +950,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="4">
-        <v>7449</v>
+        <v>17</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6455</v>
       </c>
       <c r="C16" s="4" t="e">
         <v>#N/A</v>
@@ -971,10 +967,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B17" s="5">
-        <v>6455</v>
+        <v>1025</v>
       </c>
       <c r="C17" s="4" t="e">
         <v>#N/A</v>
@@ -988,10 +984,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="B18" s="4">
-        <v>2886</v>
+        <v>3528</v>
       </c>
       <c r="C18" s="4" t="e">
         <v>#N/A</v>
@@ -1005,10 +1001,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="B19" s="5">
-        <v>1025</v>
+        <v>862</v>
       </c>
       <c r="C19" s="4" t="e">
         <v>#N/A</v>
@@ -1022,10 +1018,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B20" s="4">
-        <v>3528</v>
+        <v>168</v>
       </c>
       <c r="C20" s="4" t="e">
         <v>#N/A</v>
@@ -1039,10 +1035,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B21" s="5">
-        <v>862</v>
+        <v>5101</v>
       </c>
       <c r="C21" s="4" t="e">
         <v>#N/A</v>
@@ -1056,10 +1052,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B22" s="4">
-        <v>168</v>
+        <v>6698</v>
       </c>
       <c r="C22" s="4" t="e">
         <v>#N/A</v>
@@ -1073,10 +1069,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B23" s="5">
-        <v>5101</v>
+        <v>8128</v>
       </c>
       <c r="C23" s="4" t="e">
         <v>#N/A</v>
@@ -1090,10 +1086,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B24" s="4">
-        <v>6698</v>
+        <v>1004</v>
       </c>
       <c r="C24" s="4" t="e">
         <v>#N/A</v>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="5">
-        <v>8128</v>
+        <v>27</v>
+      </c>
+      <c r="B25" s="4">
+        <v>452</v>
       </c>
       <c r="C25" s="4" t="e">
         <v>#N/A</v>
@@ -1124,10 +1120,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B26" s="4">
-        <v>1004</v>
+        <v>9881</v>
       </c>
       <c r="C26" s="4" t="e">
         <v>#N/A</v>
@@ -1141,10 +1137,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="4">
-        <v>452</v>
+        <v>74</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2187</v>
       </c>
       <c r="C27" s="4" t="e">
         <v>#N/A</v>
@@ -1158,10 +1154,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B28" s="4">
-        <v>9881</v>
+        <v>20</v>
+      </c>
+      <c r="B28" s="5">
+        <v>7411</v>
       </c>
       <c r="C28" s="4" t="e">
         <v>#N/A</v>
@@ -1175,10 +1171,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B29" s="5">
-        <v>2187</v>
+        <v>5566</v>
       </c>
       <c r="C29" s="4" t="e">
         <v>#N/A</v>
@@ -1192,10 +1188,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="5">
-        <v>7411</v>
+        <v>33</v>
+      </c>
+      <c r="B30" s="4">
+        <v>6654</v>
       </c>
       <c r="C30" s="4" t="e">
         <v>#N/A</v>
@@ -1204,15 +1200,15 @@
         <v>#N/A</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" s="5">
-        <v>5566</v>
+        <v>30</v>
+      </c>
+      <c r="B31" s="4">
+        <v>8334</v>
       </c>
       <c r="C31" s="4" t="e">
         <v>#N/A</v>
@@ -1221,7 +1217,7 @@
         <v>#N/A</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
@@ -1238,15 +1234,15 @@
         <v>#N/A</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B33" s="4">
-        <v>6654</v>
+        <v>3481</v>
       </c>
       <c r="C33" s="4" t="e">
         <v>#N/A</v>
@@ -1260,10 +1256,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B34" s="4">
-        <v>8334</v>
+        <v>7120</v>
       </c>
       <c r="C34" s="4" t="e">
         <v>#N/A</v>
@@ -1277,10 +1273,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="B35" s="4">
-        <v>7120</v>
+        <v>2886</v>
       </c>
       <c r="C35" s="4" t="e">
         <v>#N/A</v>
@@ -1344,8 +1340,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E31">
-    <sortCondition ref="A6:A31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:E38">
+    <sortCondition ref="A30:A38"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCC99DED-23D5-43D3-B57D-30F81CC1F1AF}"/>
+  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AED8D89-8FDC-46E0-A675-EC4000C55915}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
   <si>
     <t>Name</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>DUCKs</t>
+  </si>
+  <si>
+    <t>ALOHa</t>
   </si>
 </sst>
 </file>
@@ -396,6 +399,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -683,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -780,10 +787,10 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B6" s="4">
-        <v>5161</v>
+        <v>6654</v>
       </c>
       <c r="C6" s="4" t="e">
         <v>#N/A</v>
@@ -797,10 +804,10 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4">
-        <v>3194</v>
+        <v>7510</v>
       </c>
       <c r="C7" s="4" t="e">
         <v>#N/A</v>
@@ -814,10 +821,10 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B8" s="4">
-        <v>5055</v>
+        <v>5161</v>
       </c>
       <c r="C8" s="4" t="e">
         <v>#N/A</v>
@@ -831,10 +838,10 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="5">
-        <v>7042</v>
+        <v>40</v>
+      </c>
+      <c r="B9" s="4">
+        <v>3194</v>
       </c>
       <c r="C9" s="4" t="e">
         <v>#N/A</v>
@@ -848,10 +855,10 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5">
-        <v>9706</v>
+        <v>7042</v>
       </c>
       <c r="C10" s="4" t="e">
         <v>#N/A</v>
@@ -865,10 +872,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5">
-        <v>5464</v>
+        <v>9706</v>
       </c>
       <c r="C11" s="4" t="e">
         <v>#N/A</v>
@@ -882,10 +889,10 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4">
-        <v>3480</v>
+        <v>15</v>
+      </c>
+      <c r="B12" s="5">
+        <v>5464</v>
       </c>
       <c r="C12" s="4" t="e">
         <v>#N/A</v>
@@ -899,10 +906,10 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="5">
-        <v>5078</v>
+        <v>31</v>
+      </c>
+      <c r="B13" s="4">
+        <v>3480</v>
       </c>
       <c r="C13" s="4" t="e">
         <v>#N/A</v>
@@ -916,10 +923,10 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>76</v>
+        <v>22</v>
       </c>
       <c r="B14" s="5">
-        <v>4713</v>
+        <v>5078</v>
       </c>
       <c r="C14" s="4" t="e">
         <v>#N/A</v>
@@ -933,10 +940,10 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B15" s="4">
-        <v>7449</v>
+        <v>5055</v>
       </c>
       <c r="C15" s="4" t="e">
         <v>#N/A</v>
@@ -950,10 +957,10 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="B16" s="5">
-        <v>6455</v>
+        <v>4713</v>
       </c>
       <c r="C16" s="4" t="e">
         <v>#N/A</v>
@@ -967,10 +974,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1025</v>
+        <v>73</v>
+      </c>
+      <c r="B17" s="4">
+        <v>7449</v>
       </c>
       <c r="C17" s="4" t="e">
         <v>#N/A</v>
@@ -984,10 +991,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="4">
-        <v>3528</v>
+        <v>17</v>
+      </c>
+      <c r="B18" s="5">
+        <v>6455</v>
       </c>
       <c r="C18" s="4" t="e">
         <v>#N/A</v>
@@ -1001,10 +1008,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>75</v>
+        <v>21</v>
       </c>
       <c r="B19" s="5">
-        <v>862</v>
+        <v>1025</v>
       </c>
       <c r="C19" s="4" t="e">
         <v>#N/A</v>
@@ -1018,10 +1025,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B20" s="4">
-        <v>168</v>
+        <v>3528</v>
       </c>
       <c r="C20" s="4" t="e">
         <v>#N/A</v>
@@ -1035,10 +1042,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="B21" s="5">
-        <v>5101</v>
+        <v>862</v>
       </c>
       <c r="C21" s="4" t="e">
         <v>#N/A</v>
@@ -1052,10 +1059,10 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="B22" s="4">
-        <v>6698</v>
+        <v>168</v>
       </c>
       <c r="C22" s="4" t="e">
         <v>#N/A</v>
@@ -1069,10 +1076,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B23" s="5">
-        <v>8128</v>
+        <v>5101</v>
       </c>
       <c r="C23" s="4" t="e">
         <v>#N/A</v>
@@ -1086,10 +1093,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4">
-        <v>1004</v>
+        <v>6698</v>
       </c>
       <c r="C24" s="4" t="e">
         <v>#N/A</v>
@@ -1103,10 +1110,10 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="4">
-        <v>452</v>
+        <v>18</v>
+      </c>
+      <c r="B25" s="5">
+        <v>8128</v>
       </c>
       <c r="C25" s="4" t="e">
         <v>#N/A</v>
@@ -1120,10 +1127,10 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="B26" s="4">
-        <v>9881</v>
+        <v>1004</v>
       </c>
       <c r="C26" s="4" t="e">
         <v>#N/A</v>
@@ -1137,10 +1144,10 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" s="5">
-        <v>2187</v>
+        <v>27</v>
+      </c>
+      <c r="B27" s="4">
+        <v>452</v>
       </c>
       <c r="C27" s="4" t="e">
         <v>#N/A</v>
@@ -1154,10 +1161,10 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="5">
-        <v>7411</v>
+        <v>72</v>
+      </c>
+      <c r="B28" s="4">
+        <v>9881</v>
       </c>
       <c r="C28" s="4" t="e">
         <v>#N/A</v>
@@ -1171,10 +1178,10 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B29" s="5">
-        <v>5566</v>
+        <v>2187</v>
       </c>
       <c r="C29" s="4" t="e">
         <v>#N/A</v>
@@ -1188,10 +1195,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="4">
-        <v>6654</v>
+        <v>20</v>
+      </c>
+      <c r="B30" s="5">
+        <v>7411</v>
       </c>
       <c r="C30" s="4" t="e">
         <v>#N/A</v>
@@ -1200,15 +1207,15 @@
         <v>#N/A</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="4">
-        <v>8334</v>
+        <v>24</v>
+      </c>
+      <c r="B31" s="5">
+        <v>5566</v>
       </c>
       <c r="C31" s="4" t="e">
         <v>#N/A</v>
@@ -1217,15 +1224,15 @@
         <v>#N/A</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4">
-        <v>804</v>
+        <v>8334</v>
       </c>
       <c r="C32" s="4" t="e">
         <v>#N/A</v>
@@ -1239,10 +1246,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B33" s="4">
-        <v>3481</v>
+        <v>804</v>
       </c>
       <c r="C33" s="4" t="e">
         <v>#N/A</v>
@@ -1256,10 +1263,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="B34" s="4">
-        <v>7120</v>
+        <v>3481</v>
       </c>
       <c r="C34" s="4" t="e">
         <v>#N/A</v>
@@ -1273,10 +1280,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B35" s="4">
-        <v>2886</v>
+        <v>7120</v>
       </c>
       <c r="C35" s="4" t="e">
         <v>#N/A</v>
@@ -1290,10 +1297,10 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="B36" s="4">
-        <v>2359</v>
+        <v>2886</v>
       </c>
       <c r="C36" s="4" t="e">
         <v>#N/A</v>
@@ -1307,10 +1314,10 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="4">
-        <v>3929</v>
+        <v>2359</v>
       </c>
       <c r="C37" s="4" t="e">
         <v>#N/A</v>
@@ -1324,10 +1331,10 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B38" s="4">
-        <v>5297</v>
+        <v>3929</v>
       </c>
       <c r="C38" s="4" t="e">
         <v>#N/A</v>
@@ -1339,9 +1346,26 @@
         <v>69</v>
       </c>
     </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" s="4">
+        <v>5297</v>
+      </c>
+      <c r="C39" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D39" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A30:E38">
-    <sortCondition ref="A30:A38"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:E31">
+    <sortCondition ref="A6:A31"/>
   </sortState>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="206" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8AED8D89-8FDC-46E0-A675-EC4000C55915}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB2AD266-7884-4B2E-A706-811AC7E6097B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,9 +256,6 @@
     <t>Souta メ</t>
   </si>
   <si>
-    <t>iCatzilla</t>
-  </si>
-  <si>
     <t>SwallowTaiL</t>
   </si>
   <si>
@@ -269,6 +266,9 @@
   </si>
   <si>
     <t>ALOHa</t>
+  </si>
+  <si>
+    <t>Catzilla</t>
   </si>
 </sst>
 </file>
@@ -804,7 +804,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B7" s="4">
         <v>7510</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5">
         <v>4713</v>
@@ -974,7 +974,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B17" s="4">
         <v>7449</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="5">
         <v>862</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29" s="5">
         <v>2187</v>

--- a/data/master.xlsx
+++ b/data/master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a225a4cd7e80232/Wasawat/Etheria/gvgplaner/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB2AD266-7884-4B2E-A706-811AC7E6097B}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="13_ncr:1_{FB02597B-DDFD-481B-B7DE-A53AD49E1F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97D5A35F-FF5F-4CF9-AD9B-D268172A6B16}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="79">
   <si>
     <t>Name</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Catzilla</t>
+  </si>
+  <si>
+    <t>GGood</t>
   </si>
 </sst>
 </file>
@@ -690,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -1025,10 +1028,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="4">
-        <v>3528</v>
+        <v>78</v>
+      </c>
+      <c r="B20" s="5">
+        <v>6612</v>
       </c>
       <c r="C20" s="4" t="e">
         <v>#N/A</v>
@@ -1360,6 +1363,23 @@
         <v>#N/A</v>
       </c>
       <c r="E39" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40" s="4">
+        <v>3528</v>
+      </c>
+      <c r="C40" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D40" s="4" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>69</v>
       </c>
     </row>
